--- a/data/trans_orig/P6708-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6708-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se tiene en cuenta su opinión cuando se le asignan las tareas en 2012</t>
+          <t>Población según si se tiene en cuenta su opinión cuando se le asignan las tareas en 2012 (tasa de respuesta: 99,1%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10917</t>
+          <t>11848</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30667</t>
+          <t>30491</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21814</t>
+          <t>21149</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21315</t>
+          <t>22076</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43683</t>
+          <t>44484</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8841</t>
+          <t>8706</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25343</t>
+          <t>25208</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5858</t>
+          <t>5155</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19194</t>
+          <t>18930</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17853</t>
+          <t>16644</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39330</t>
+          <t>39144</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40588</t>
+          <t>39910</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>66721</t>
+          <t>65699</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22535</t>
+          <t>21475</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43914</t>
+          <t>43449</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>69099</t>
+          <t>69357</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>101769</t>
+          <t>102675</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,92%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54005</t>
+          <t>54053</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83415</t>
+          <t>83753</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28566</t>
+          <t>29552</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51170</t>
+          <t>50921</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>89355</t>
+          <t>88992</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>126118</t>
+          <t>126306</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,42%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>95503</t>
+          <t>97178</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>130179</t>
+          <t>129389</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>54417</t>
+          <t>56136</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79776</t>
+          <t>80189</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>159463</t>
+          <t>157964</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>199209</t>
+          <t>199353</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,44%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19689</t>
+          <t>19301</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43374</t>
+          <t>44490</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15500</t>
+          <t>15084</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36084</t>
+          <t>33862</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38225</t>
+          <t>40227</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67123</t>
+          <t>69533</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17994</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40222</t>
+          <t>40033</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15287</t>
+          <t>15548</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34531</t>
+          <t>33361</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37369</t>
+          <t>37326</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>66386</t>
+          <t>67144</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>68236</t>
+          <t>70455</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>100166</t>
+          <t>103876</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43901</t>
+          <t>43986</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71023</t>
+          <t>71851</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>120083</t>
+          <t>121523</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>163372</t>
+          <t>164663</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,28%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77455</t>
+          <t>78628</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>112195</t>
+          <t>112587</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44022</t>
+          <t>43493</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70600</t>
+          <t>71872</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>128127</t>
+          <t>131773</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>172763</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,73%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>154416</t>
+          <t>153044</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>197044</t>
+          <t>194865</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>92551</t>
+          <t>92963</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>126309</t>
+          <t>126049</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>258224</t>
+          <t>257019</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>311892</t>
+          <t>309487</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,64%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13799</t>
+          <t>14680</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33017</t>
+          <t>35174</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16342</t>
+          <t>16375</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35648</t>
+          <t>36314</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35408</t>
+          <t>36604</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63848</t>
+          <t>63005</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20625</t>
+          <t>20954</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44376</t>
+          <t>42722</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8014</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24986</t>
+          <t>24027</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31808</t>
+          <t>33445</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60918</t>
+          <t>60519</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>40018</t>
+          <t>39641</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>68890</t>
+          <t>65743</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25740</t>
+          <t>25203</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>48898</t>
+          <t>49433</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>73823</t>
+          <t>71778</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>111290</t>
+          <t>108805</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54497</t>
+          <t>54519</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86419</t>
+          <t>86783</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40666</t>
+          <t>40410</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67058</t>
+          <t>67491</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>102219</t>
+          <t>102195</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>141805</t>
+          <t>141884</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,58%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>127014</t>
+          <t>126835</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>164199</t>
+          <t>164543</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>70292</t>
+          <t>71744</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>100963</t>
+          <t>101600</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>205478</t>
+          <t>207165</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>255207</t>
+          <t>254662</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>47,71%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24018</t>
+          <t>23837</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47959</t>
+          <t>48604</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19343</t>
+          <t>20324</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42260</t>
+          <t>42097</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>49367</t>
+          <t>48642</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>81228</t>
+          <t>81440</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22924</t>
+          <t>23186</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>47259</t>
+          <t>46631</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>19657</t>
+          <t>19370</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>40385</t>
+          <t>40894</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>47692</t>
+          <t>48831</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>77420</t>
+          <t>79610</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>80159</t>
+          <t>81432</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>113905</t>
+          <t>115361</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>59182</t>
+          <t>61491</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>91055</t>
+          <t>95219</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>149643</t>
+          <t>151950</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>200279</t>
+          <t>198748</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,63%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>100391</t>
+          <t>99282</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>137757</t>
+          <t>135152</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>63452</t>
+          <t>62567</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>93488</t>
+          <t>93020</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>170285</t>
+          <t>173229</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>219371</t>
+          <t>220594</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,67%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>117406</t>
+          <t>117656</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>157062</t>
+          <t>155943</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>72350</t>
+          <t>73293</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>105471</t>
+          <t>105432</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>199660</t>
+          <t>198449</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>253293</t>
+          <t>249815</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>34,73%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>87223</t>
+          <t>87716</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>129108</t>
+          <t>128823</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>73322</t>
+          <t>72402</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>108786</t>
+          <t>108590</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>170383</t>
+          <t>169705</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>224705</t>
+          <t>226599</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>87043</t>
+          <t>86457</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>128232</t>
+          <t>129721</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>60461</t>
+          <t>62846</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>94643</t>
+          <t>96407</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>157553</t>
+          <t>158530</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>210271</t>
+          <t>213647</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>258352</t>
+          <t>256732</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>321852</t>
+          <t>319024</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>176047</t>
+          <t>177376</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>228996</t>
+          <t>230250</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>451893</t>
+          <t>449964</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>533979</t>
+          <t>533697</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,61%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>313279</t>
+          <t>314598</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>379620</t>
+          <t>382109</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>201689</t>
+          <t>198330</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>254692</t>
+          <t>253894</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>530448</t>
+          <t>532542</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>616471</t>
+          <t>619180</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,23%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>527442</t>
+          <t>530960</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>604958</t>
+          <t>603346</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>320206</t>
+          <t>316610</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>382386</t>
+          <t>379608</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>866830</t>
+          <t>867141</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>964151</t>
+          <t>968930</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>41,05%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se tiene en cuenta su opinión cuando se le asignan las tareas en 2016</t>
+          <t>Población según si se tiene en cuenta su opinión cuando se le asignan las tareas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18504</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38549</t>
+          <t>39558</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20546</t>
+          <t>21372</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39767</t>
+          <t>40446</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45270</t>
+          <t>45445</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75730</t>
+          <t>72282</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>17,6%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24879</t>
+          <t>24902</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45715</t>
+          <t>46999</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13825</t>
+          <t>13682</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31233</t>
+          <t>30285</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43493</t>
+          <t>42202</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>70736</t>
+          <t>69941</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,03%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42448</t>
+          <t>43236</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>69595</t>
+          <t>69933</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21268</t>
+          <t>20903</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39874</t>
+          <t>39187</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>70480</t>
+          <t>71270</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>101643</t>
+          <t>103737</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>25,26%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41981</t>
+          <t>42852</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67858</t>
+          <t>69634</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43386</t>
+          <t>43311</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67131</t>
+          <t>66786</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>92360</t>
+          <t>92501</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>130399</t>
+          <t>127109</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>30,95%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>56701</t>
+          <t>56659</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84177</t>
+          <t>87096</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23349</t>
+          <t>23170</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>42424</t>
+          <t>42924</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>85170</t>
+          <t>83823</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>120305</t>
+          <t>120193</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,27%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18282</t>
+          <t>18785</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39575</t>
+          <t>40457</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22089</t>
+          <t>22699</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43379</t>
+          <t>44545</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45953</t>
+          <t>45449</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>76495</t>
+          <t>76389</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49744</t>
+          <t>49795</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>81404</t>
+          <t>80780</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33683</t>
+          <t>33851</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56134</t>
+          <t>58094</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>88734</t>
+          <t>88944</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>127598</t>
+          <t>128921</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,74%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>94967</t>
+          <t>95988</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>134577</t>
+          <t>133311</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>50971</t>
+          <t>50973</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>78825</t>
+          <t>79276</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>154716</t>
+          <t>153925</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>201272</t>
+          <t>202383</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,42%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74136</t>
+          <t>74484</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>110744</t>
+          <t>108203</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57869</t>
+          <t>56388</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>86266</t>
+          <t>86096</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>140111</t>
+          <t>139057</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>185771</t>
+          <t>188397</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,39%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>97992</t>
+          <t>99773</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>137960</t>
+          <t>139246</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50081</t>
+          <t>49703</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76854</t>
+          <t>76927</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>157631</t>
+          <t>157400</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>204811</t>
+          <t>205326</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,85%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28122</t>
+          <t>29042</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>52427</t>
+          <t>55026</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11804</t>
+          <t>11492</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27768</t>
+          <t>27951</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45202</t>
+          <t>43627</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74123</t>
+          <t>72851</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37615</t>
+          <t>38777</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>65440</t>
+          <t>65813</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34463</t>
+          <t>34078</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57696</t>
+          <t>60618</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>78318</t>
+          <t>78957</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>114769</t>
+          <t>113816</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>103479</t>
+          <t>101904</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>139550</t>
+          <t>139571</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,47 +5979,47 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
+          <t>28,01%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>38,36%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>90807</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>76957</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>106436</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>33,56%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
           <t>28,44%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>38,36%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>90807</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>75276</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>105734</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>33,56%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>27,82%</t>
-        </is>
-      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>189487</t>
+          <t>187233</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>234862</t>
+          <t>235713</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,16%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>63983</t>
+          <t>62238</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>95101</t>
+          <t>94800</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42604</t>
+          <t>41124</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>68708</t>
+          <t>67842</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>111731</t>
+          <t>111898</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>154576</t>
+          <t>154952</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,43%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>58106</t>
+          <t>60033</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>88731</t>
+          <t>91435</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48332</t>
+          <t>48428</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>76127</t>
+          <t>75645</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>113980</t>
+          <t>115866</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>157950</t>
+          <t>158859</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,04%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28960</t>
+          <t>28851</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52674</t>
+          <t>52869</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28340</t>
+          <t>29398</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53478</t>
+          <t>54218</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>64017</t>
+          <t>65153</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>97503</t>
+          <t>99336</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,67%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34435</t>
+          <t>33837</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>59661</t>
+          <t>58907</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>35735</t>
+          <t>35119</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>60845</t>
+          <t>61700</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>76564</t>
+          <t>75917</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>113673</t>
+          <t>110937</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,27%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>87832</t>
+          <t>88889</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>124247</t>
+          <t>123749</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>73977</t>
+          <t>73487</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>104792</t>
+          <t>105376</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>170805</t>
+          <t>171405</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>219694</t>
+          <t>219136</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,16%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>81864</t>
+          <t>83115</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>116284</t>
+          <t>119220</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>48099</t>
+          <t>47816</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>77269</t>
+          <t>76339</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>139035</t>
+          <t>139130</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>182440</t>
+          <t>185015</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,46%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>93933</t>
+          <t>93630</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>131121</t>
+          <t>129373</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>72124</t>
+          <t>71885</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>103265</t>
+          <t>105333</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>174908</t>
+          <t>173901</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>225263</t>
+          <t>222416</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,61%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>114745</t>
+          <t>111470</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>163783</t>
+          <t>158323</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>99393</t>
+          <t>98291</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>141252</t>
+          <t>140422</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>225818</t>
+          <t>225940</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>288180</t>
+          <t>291613</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>169316</t>
+          <t>168945</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>220996</t>
+          <t>222879</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>136306</t>
+          <t>137964</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>181745</t>
+          <t>185023</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>319379</t>
+          <t>318829</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>393783</t>
+          <t>391166</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,9%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>362412</t>
+          <t>365109</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>429735</t>
+          <t>435417</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>244665</t>
+          <t>245907</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>304915</t>
+          <t>306060</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>625082</t>
+          <t>626402</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>717156</t>
+          <t>716447</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,13%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>291982</t>
+          <t>291051</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>356172</t>
+          <t>356502</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>213551</t>
+          <t>216479</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>268129</t>
+          <t>270438</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>525050</t>
+          <t>523426</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>608722</t>
+          <t>604194</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,57%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>343054</t>
+          <t>341227</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>410940</t>
+          <t>412121</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>219858</t>
+          <t>216723</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>274408</t>
+          <t>272371</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>571363</t>
+          <t>571537</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>658396</t>
+          <t>660647</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,86%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se tiene en cuenta su opinión cuando se le asignan las tareas en 2023</t>
+          <t>Población según si se tiene en cuenta su opinión cuando se le asignan las tareas en 2023 (tasa de respuesta: 99,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2997</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16568</t>
+          <t>16209</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>7068</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18326</t>
+          <t>18509</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12274</t>
+          <t>12007</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29326</t>
+          <t>29306</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,85%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2941</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14113</t>
+          <t>14373</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14350</t>
+          <t>14959</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8072</t>
+          <t>8790</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23920</t>
+          <t>24741</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16820</t>
+          <t>17397</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41640</t>
+          <t>41707</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13197</t>
+          <t>13076</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25561</t>
+          <t>26224</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>33738</t>
+          <t>33464</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>62143</t>
+          <t>61091</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,3%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>10046</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25625</t>
+          <t>25677</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t>7486</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18179</t>
+          <t>17913</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20446</t>
+          <t>20582</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38815</t>
+          <t>39169</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,2%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16724</t>
+          <t>16622</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39094</t>
+          <t>40644</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11715</t>
+          <t>11424</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27217</t>
+          <t>25930</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>33580</t>
+          <t>33528</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>61746</t>
+          <t>61273</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,42%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33905</t>
+          <t>32865</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15367</t>
+          <t>15401</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28921</t>
+          <t>29564</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10193</t>
+          <t>9082</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67187</t>
+          <t>68660</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6381</t>
+          <t>5737</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>81838</t>
+          <t>82009</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7054</t>
+          <t>6683</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18383</t>
+          <t>18446</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12610</t>
+          <t>11772</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>85860</t>
+          <t>83676</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,35%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12600</t>
+          <t>13084</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>129618</t>
+          <t>128796</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30584</t>
+          <t>30883</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>49328</t>
+          <t>48436</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>25602</t>
+          <t>25780</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>168354</t>
+          <t>169027</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,03%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6024</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83519</t>
+          <t>80501</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13752</t>
+          <t>13426</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29188</t>
+          <t>29240</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16101</t>
+          <t>14542</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>102371</t>
+          <t>100412</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92556</t>
+          <t>92273</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>362018</t>
+          <t>361541</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15715</t>
+          <t>15709</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31576</t>
+          <t>30903</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>108215</t>
+          <t>108388</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>442494</t>
+          <t>441303</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,25%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8057</t>
+          <t>8228</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23024</t>
+          <t>23048</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10924</t>
+          <t>10933</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24295</t>
+          <t>23960</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22348</t>
+          <t>22050</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42189</t>
+          <t>42174</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,72%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6506</t>
+          <t>7132</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22222</t>
+          <t>23856</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8885</t>
+          <t>8761</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20797</t>
+          <t>21992</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18180</t>
+          <t>17706</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37674</t>
+          <t>37994</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,07%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12769</t>
+          <t>11973</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30353</t>
+          <t>29139</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15485</t>
+          <t>15450</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29502</t>
+          <t>29907</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>31381</t>
+          <t>29839</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>54805</t>
+          <t>52970</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>33,56%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6973</t>
+          <t>6458</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21508</t>
+          <t>22051</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8261</t>
+          <t>8285</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19896</t>
+          <t>20021</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17914</t>
+          <t>17856</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36485</t>
+          <t>37031</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9528</t>
+          <t>8533</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26075</t>
+          <t>25530</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10106</t>
+          <t>9931</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22076</t>
+          <t>22081</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>22478</t>
+          <t>22839</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>42355</t>
+          <t>42470</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,91%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21114</t>
+          <t>20648</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41170</t>
+          <t>41176</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15792</t>
+          <t>16520</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30274</t>
+          <t>30827</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40817</t>
+          <t>41525</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65490</t>
+          <t>66284</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>34,05%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3829</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15563</t>
+          <t>16433</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>7852</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>18948</t>
+          <t>19457</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>13862</t>
+          <t>14053</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>29663</t>
+          <t>30472</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21557</t>
+          <t>21750</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>40761</t>
+          <t>40833</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>8856</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20791</t>
+          <t>20584</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>34512</t>
+          <t>34894</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>57558</t>
+          <t>57663</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,62%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11200</t>
+          <t>10260</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27519</t>
+          <t>26969</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14925</t>
+          <t>14568</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29156</t>
+          <t>28738</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>29183</t>
+          <t>28990</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>51647</t>
+          <t>51234</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,32%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13397</t>
+          <t>13460</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>29922</t>
+          <t>31058</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10632</t>
+          <t>11003</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22896</t>
+          <t>22581</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>27928</t>
+          <t>27394</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>48316</t>
+          <t>48545</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,94%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>22968</t>
+          <t>20736</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>107167</t>
+          <t>107499</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>59531</t>
+          <t>60567</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>86037</t>
+          <t>88193</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>61891</t>
+          <t>66547</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>185363</t>
+          <t>189120</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,55%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>18817</t>
+          <t>18382</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>98275</t>
+          <t>99146</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>35035</t>
+          <t>36178</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>58128</t>
+          <t>59361</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>51265</t>
+          <t>51962</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>145594</t>
+          <t>145582</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,7 +10942,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>48965</t>
+          <t>43408</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>204245</t>
+          <t>209438</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>79206</t>
+          <t>80545</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>107405</t>
+          <t>109631</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>118144</t>
+          <t>103820</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>294611</t>
+          <t>297539</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,18%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>29074</t>
+          <t>28559</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>128703</t>
+          <t>128189</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>56535</t>
+          <t>55006</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>82799</t>
+          <t>80689</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>70851</t>
+          <t>69844</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>197802</t>
+          <t>194456</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,07%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>155219</t>
+          <t>155233</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>541052</t>
+          <t>556149</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>58913</t>
+          <t>58402</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>86940</t>
+          <t>86973</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>224178</t>
+          <t>222513</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>705700</t>
+          <t>704705</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,12%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6708-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6708-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11848</t>
+          <t>11623</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30491</t>
+          <t>30152</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>6961</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21149</t>
+          <t>21373</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22076</t>
+          <t>22038</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44484</t>
+          <t>47149</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8706</t>
+          <t>8665</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25208</t>
+          <t>25413</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5155</t>
+          <t>5140</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18930</t>
+          <t>18747</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16644</t>
+          <t>16744</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39144</t>
+          <t>38091</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39910</t>
+          <t>41039</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>65699</t>
+          <t>66907</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21475</t>
+          <t>21882</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43449</t>
+          <t>42947</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>69357</t>
+          <t>69028</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>102675</t>
+          <t>103381</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,08%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54053</t>
+          <t>53013</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83753</t>
+          <t>83599</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29552</t>
+          <t>29064</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50921</t>
+          <t>51671</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>88992</t>
+          <t>90507</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>126306</t>
+          <t>125748</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,29%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>97178</t>
+          <t>97509</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>129389</t>
+          <t>130572</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>56136</t>
+          <t>54706</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80189</t>
+          <t>80643</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>157964</t>
+          <t>158657</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>199353</t>
+          <t>198771</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>46,3%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19301</t>
+          <t>19306</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44490</t>
+          <t>43369</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15084</t>
+          <t>14909</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33862</t>
+          <t>34997</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40227</t>
+          <t>38505</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69533</t>
+          <t>69285</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17994</t>
+          <t>17830</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40033</t>
+          <t>39069</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15548</t>
+          <t>14450</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33361</t>
+          <t>33158</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37326</t>
+          <t>36833</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>67144</t>
+          <t>65981</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>70455</t>
+          <t>69647</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>103876</t>
+          <t>104141</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43986</t>
+          <t>43225</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71851</t>
+          <t>71200</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>121523</t>
+          <t>120761</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>164663</t>
+          <t>165123</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,35%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78628</t>
+          <t>76518</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>112587</t>
+          <t>112122</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43493</t>
+          <t>42654</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71872</t>
+          <t>69644</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>131773</t>
+          <t>128722</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>174460</t>
+          <t>174282</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,7%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>153044</t>
+          <t>153875</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>194865</t>
+          <t>194235</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>92963</t>
+          <t>92112</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>126049</t>
+          <t>127088</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>257019</t>
+          <t>258356</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>309487</t>
+          <t>309535</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,65%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14680</t>
+          <t>14071</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35174</t>
+          <t>34425</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16375</t>
+          <t>16474</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36314</t>
+          <t>35751</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36604</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63005</t>
+          <t>61987</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20954</t>
+          <t>20923</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42722</t>
+          <t>44762</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7721</t>
+          <t>7589</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24027</t>
+          <t>24734</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33445</t>
+          <t>32451</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60519</t>
+          <t>60085</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>39641</t>
+          <t>40279</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>65743</t>
+          <t>67197</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25203</t>
+          <t>26140</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>49433</t>
+          <t>49212</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>71778</t>
+          <t>72765</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>108805</t>
+          <t>108607</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,35%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54519</t>
+          <t>53988</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86783</t>
+          <t>84228</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40410</t>
+          <t>41421</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67491</t>
+          <t>66332</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>102195</t>
+          <t>102330</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>141884</t>
+          <t>142324</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,66%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>126835</t>
+          <t>126209</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>164543</t>
+          <t>163158</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>71744</t>
+          <t>71439</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>101600</t>
+          <t>100666</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>207165</t>
+          <t>206414</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>254662</t>
+          <t>252459</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,29%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23837</t>
+          <t>24917</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48604</t>
+          <t>47837</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20324</t>
+          <t>20153</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42097</t>
+          <t>43235</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>48642</t>
+          <t>51073</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>81440</t>
+          <t>82965</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23186</t>
+          <t>23905</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>46631</t>
+          <t>45864</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>19370</t>
+          <t>19960</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>40894</t>
+          <t>40782</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>48831</t>
+          <t>49034</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>79610</t>
+          <t>78044</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>81432</t>
+          <t>80731</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>115361</t>
+          <t>117728</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>61491</t>
+          <t>62449</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>95219</t>
+          <t>95046</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>151950</t>
+          <t>151674</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>198748</t>
+          <t>199128</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,69%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>99282</t>
+          <t>96851</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>135152</t>
+          <t>134389</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>62567</t>
+          <t>63266</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>93020</t>
+          <t>94996</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>173229</t>
+          <t>171490</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>220594</t>
+          <t>218184</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,33%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>117656</t>
+          <t>117429</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>155943</t>
+          <t>156214</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>73293</t>
+          <t>72266</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>105432</t>
+          <t>104966</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>198449</t>
+          <t>199465</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>249815</t>
+          <t>251167</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,92%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>87716</t>
+          <t>87866</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>128823</t>
+          <t>127920</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>72402</t>
+          <t>73136</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>108590</t>
+          <t>109647</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>169705</t>
+          <t>172520</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>226599</t>
+          <t>225193</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>86457</t>
+          <t>85690</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>129721</t>
+          <t>126776</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>62846</t>
+          <t>61389</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>96407</t>
+          <t>96481</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>158530</t>
+          <t>157417</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>213647</t>
+          <t>211253</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>256732</t>
+          <t>256565</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>319024</t>
+          <t>319787</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>177376</t>
+          <t>176436</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>230250</t>
+          <t>230465</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>449964</t>
+          <t>451553</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>533697</t>
+          <t>535199</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>314598</t>
+          <t>313882</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>382109</t>
+          <t>379805</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>198330</t>
+          <t>201588</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>253894</t>
+          <t>253555</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>532542</t>
+          <t>529930</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>619180</t>
+          <t>616417</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,12%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>530960</t>
+          <t>531410</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>603346</t>
+          <t>606923</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>316610</t>
+          <t>318820</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>379608</t>
+          <t>380454</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>867141</t>
+          <t>870150</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>968930</t>
+          <t>969452</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,07%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>19406</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39558</t>
+          <t>39717</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21372</t>
+          <t>22544</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40446</t>
+          <t>41911</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45445</t>
+          <t>44944</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72282</t>
+          <t>72046</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,54%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24902</t>
+          <t>25818</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46999</t>
+          <t>47685</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13682</t>
+          <t>14103</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30285</t>
+          <t>31549</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42202</t>
+          <t>41442</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69941</t>
+          <t>68484</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,68%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43236</t>
+          <t>43483</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>69933</t>
+          <t>70475</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20903</t>
+          <t>20712</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39187</t>
+          <t>39345</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>71270</t>
+          <t>69325</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>103737</t>
+          <t>100669</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,51%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42852</t>
+          <t>41677</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69634</t>
+          <t>68499</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43311</t>
+          <t>43052</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66786</t>
+          <t>65696</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>92501</t>
+          <t>92622</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>127109</t>
+          <t>128343</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,25%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>56659</t>
+          <t>56769</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>87096</t>
+          <t>85643</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23170</t>
+          <t>23168</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>42924</t>
+          <t>43522</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>83823</t>
+          <t>86568</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>120193</t>
+          <t>123694</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>30,12%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18785</t>
+          <t>18547</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40457</t>
+          <t>40981</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22699</t>
+          <t>22881</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44545</t>
+          <t>44190</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45449</t>
+          <t>45909</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>76389</t>
+          <t>74661</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49795</t>
+          <t>50447</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80780</t>
+          <t>79840</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33851</t>
+          <t>32877</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>58094</t>
+          <t>57087</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>88944</t>
+          <t>87721</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>128921</t>
+          <t>127413</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>95988</t>
+          <t>95806</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>133311</t>
+          <t>133746</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>50973</t>
+          <t>51114</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>79276</t>
+          <t>78431</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>153925</t>
+          <t>154671</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>202383</t>
+          <t>199540</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,01%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74484</t>
+          <t>72844</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>108203</t>
+          <t>108869</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56388</t>
+          <t>56951</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>86096</t>
+          <t>86220</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>139057</t>
+          <t>140198</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>188397</t>
+          <t>185428</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>26,96%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99773</t>
+          <t>99797</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>139246</t>
+          <t>138828</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49703</t>
+          <t>48646</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76927</t>
+          <t>77147</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>157400</t>
+          <t>159810</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>205326</t>
+          <t>207485</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,17%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29042</t>
+          <t>28341</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55026</t>
+          <t>54932</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11492</t>
+          <t>11638</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27951</t>
+          <t>27686</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43627</t>
+          <t>44518</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72851</t>
+          <t>73883</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38777</t>
+          <t>38311</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>65813</t>
+          <t>66880</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34078</t>
+          <t>34723</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>60618</t>
+          <t>61700</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>78957</t>
+          <t>78615</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>113816</t>
+          <t>115564</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>101904</t>
+          <t>103842</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>139571</t>
+          <t>141565</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>76957</t>
+          <t>76361</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>106436</t>
+          <t>105857</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>187233</t>
+          <t>187522</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>235713</t>
+          <t>235959</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,2%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>62238</t>
+          <t>63125</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>94800</t>
+          <t>95458</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41124</t>
+          <t>41684</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67842</t>
+          <t>67230</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>111898</t>
+          <t>110513</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>154952</t>
+          <t>153366</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,18%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>60033</t>
+          <t>58824</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>91435</t>
+          <t>90899</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48428</t>
+          <t>49289</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>75645</t>
+          <t>76652</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>115866</t>
+          <t>115546</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>158859</t>
+          <t>157917</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,89%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28851</t>
+          <t>28687</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52869</t>
+          <t>54875</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29398</t>
+          <t>29267</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54218</t>
+          <t>54186</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>65153</t>
+          <t>63842</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>99336</t>
+          <t>98185</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>33837</t>
+          <t>33257</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>58907</t>
+          <t>59328</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>35119</t>
+          <t>35389</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>61700</t>
+          <t>60597</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>75917</t>
+          <t>76915</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>110937</t>
+          <t>113463</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,61%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>88889</t>
+          <t>87973</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>123749</t>
+          <t>124722</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>73487</t>
+          <t>74508</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>105376</t>
+          <t>106422</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>171405</t>
+          <t>171857</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>219136</t>
+          <t>218449</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,06%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>83115</t>
+          <t>83641</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>119220</t>
+          <t>120268</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>47816</t>
+          <t>48523</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>76339</t>
+          <t>76264</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>139130</t>
+          <t>139108</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>185015</t>
+          <t>184944</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>93630</t>
+          <t>94653</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>129373</t>
+          <t>129762</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>71885</t>
+          <t>71567</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>105333</t>
+          <t>104433</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>173901</t>
+          <t>174937</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>222416</t>
+          <t>225282</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>31,0%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>111470</t>
+          <t>115045</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>158323</t>
+          <t>159809</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>98291</t>
+          <t>102682</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>140422</t>
+          <t>143918</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>225940</t>
+          <t>226184</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>291613</t>
+          <t>290593</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>168945</t>
+          <t>169342</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>222879</t>
+          <t>225716</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>137964</t>
+          <t>137614</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>185023</t>
+          <t>181503</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>318829</t>
+          <t>320282</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>391166</t>
+          <t>390053</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,86%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>365109</t>
+          <t>362278</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>435417</t>
+          <t>432344</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>245907</t>
+          <t>245147</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>306060</t>
+          <t>302047</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>626402</t>
+          <t>626016</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>716447</t>
+          <t>717002</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,15%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>291051</t>
+          <t>290191</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>356502</t>
+          <t>353681</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>216479</t>
+          <t>215111</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>270438</t>
+          <t>269279</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>523426</t>
+          <t>523557</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>604194</t>
+          <t>605259</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,61%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>341227</t>
+          <t>343117</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>412121</t>
+          <t>406400</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>216723</t>
+          <t>216926</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>272371</t>
+          <t>272682</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>571537</t>
+          <t>573316</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>660647</t>
+          <t>665831</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>27,07%</t>
         </is>
       </c>
     </row>
@@ -8011,32 +8011,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7592</t>
+          <t>11194</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>4511</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16209</t>
+          <t>20917</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8046,32 +8046,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11855</t>
+          <t>14871</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7068</t>
+          <t>8092</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18509</t>
+          <t>22548</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8081,32 +8081,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>19447</t>
+          <t>26066</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12007</t>
+          <t>17248</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29306</t>
+          <t>37938</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>21,84%</t>
         </is>
       </c>
     </row>
@@ -8124,32 +8124,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7494</t>
+          <t>8397</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3676</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14373</t>
+          <t>15341</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8159,22 +8159,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7649</t>
+          <t>8955</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>4044</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14959</t>
+          <t>15710</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8194,32 +8194,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>15143</t>
+          <t>17352</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8790</t>
+          <t>10490</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24741</t>
+          <t>28346</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -8237,32 +8237,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>27628</t>
+          <t>26546</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17397</t>
+          <t>16869</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41707</t>
+          <t>40290</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8272,32 +8272,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18311</t>
+          <t>19776</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13076</t>
+          <t>13361</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26224</t>
+          <t>27734</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8307,32 +8307,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>45940</t>
+          <t>46322</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>33464</t>
+          <t>34742</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>61091</t>
+          <t>60784</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>34,99%</t>
         </is>
       </c>
     </row>
@@ -8350,32 +8350,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17204</t>
+          <t>19163</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10046</t>
+          <t>12087</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25677</t>
+          <t>28979</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8385,32 +8385,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12107</t>
+          <t>13086</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7486</t>
+          <t>8314</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17913</t>
+          <t>19425</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8420,32 +8420,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>29311</t>
+          <t>32249</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20582</t>
+          <t>23623</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39169</t>
+          <t>43912</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,28%</t>
         </is>
       </c>
     </row>
@@ -8463,32 +8463,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>27582</t>
+          <t>31267</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16622</t>
+          <t>20775</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40644</t>
+          <t>45065</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8498,32 +8498,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>18006</t>
+          <t>20458</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11424</t>
+          <t>13145</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25930</t>
+          <t>29792</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8533,32 +8533,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>45589</t>
+          <t>51725</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>33528</t>
+          <t>38914</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>61273</t>
+          <t>68226</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,28%</t>
         </is>
       </c>
     </row>
@@ -8576,17 +8576,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>87500</t>
+          <t>96567</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>87500</t>
+          <t>96567</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>87500</t>
+          <t>96567</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8611,17 +8611,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>67928</t>
+          <t>77146</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>67928</t>
+          <t>77146</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>67928</t>
+          <t>77146</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8646,17 +8646,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>155429</t>
+          <t>173713</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>155429</t>
+          <t>173713</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>155429</t>
+          <t>173713</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8693,32 +8693,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10716</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>5867</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32865</t>
+          <t>21313</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8728,32 +8728,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>21427</t>
+          <t>25637</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15401</t>
+          <t>18386</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29564</t>
+          <t>34903</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8763,32 +8763,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>32144</t>
+          <t>37028</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9082</t>
+          <t>27219</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68660</t>
+          <t>50310</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -8806,32 +8806,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>27996</t>
+          <t>29521</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5737</t>
+          <t>19409</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>82009</t>
+          <t>43561</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8841,32 +8841,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11758</t>
+          <t>12539</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6683</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18446</t>
+          <t>20097</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8876,32 +8876,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>39754</t>
+          <t>42060</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11772</t>
+          <t>30111</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>83676</t>
+          <t>58132</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -8919,32 +8919,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>45689</t>
+          <t>53662</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13084</t>
+          <t>40177</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>128796</t>
+          <t>67397</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8954,32 +8954,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>39396</t>
+          <t>42117</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30883</t>
+          <t>33561</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48436</t>
+          <t>51663</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8989,32 +8989,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>85084</t>
+          <t>95778</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>25780</t>
+          <t>78617</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>169027</t>
+          <t>113721</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>38,07%</t>
         </is>
       </c>
     </row>
@@ -9032,32 +9032,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28670</t>
+          <t>30941</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>21830</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80501</t>
+          <t>43682</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9067,32 +9067,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20111</t>
+          <t>21290</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13426</t>
+          <t>14773</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29240</t>
+          <t>31330</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9102,32 +9102,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>48780</t>
+          <t>52231</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14542</t>
+          <t>39487</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>100412</t>
+          <t>66172</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>22,15%</t>
         </is>
       </c>
     </row>
@@ -9145,32 +9145,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>283499</t>
+          <t>46384</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92273</t>
+          <t>34660</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>361541</t>
+          <t>60267</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9180,32 +9180,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>22407</t>
+          <t>25240</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15709</t>
+          <t>17240</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30903</t>
+          <t>34145</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9215,32 +9215,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>305907</t>
+          <t>71625</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>108388</t>
+          <t>54777</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>441303</t>
+          <t>88247</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>29,54%</t>
         </is>
       </c>
     </row>
@@ -9258,17 +9258,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>396570</t>
+          <t>171899</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>396570</t>
+          <t>171899</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>396570</t>
+          <t>171899</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9293,17 +9293,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>115099</t>
+          <t>126823</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>115099</t>
+          <t>126823</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>115099</t>
+          <t>126823</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9328,17 +9328,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>511669</t>
+          <t>298722</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>511669</t>
+          <t>298722</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>511669</t>
+          <t>298722</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9375,32 +9375,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14578</t>
+          <t>22461</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8228</t>
+          <t>13558</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23048</t>
+          <t>35472</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9410,32 +9410,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>16824</t>
+          <t>20472</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10933</t>
+          <t>13501</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23960</t>
+          <t>28092</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9445,32 +9445,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>31402</t>
+          <t>42933</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22050</t>
+          <t>31869</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42174</t>
+          <t>58938</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>31,92%</t>
         </is>
       </c>
     </row>
@@ -9488,32 +9488,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12931</t>
+          <t>15814</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>8587</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23856</t>
+          <t>26514</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9523,32 +9523,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13919</t>
+          <t>17137</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8761</t>
+          <t>11086</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21992</t>
+          <t>24969</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9558,32 +9558,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>26850</t>
+          <t>32952</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17706</t>
+          <t>21517</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37994</t>
+          <t>46346</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -9601,32 +9601,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19961</t>
+          <t>22383</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11973</t>
+          <t>13534</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29139</t>
+          <t>33542</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9636,32 +9636,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>21606</t>
+          <t>24220</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15450</t>
+          <t>17035</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29907</t>
+          <t>32461</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9671,32 +9671,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>41567</t>
+          <t>46603</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>29839</t>
+          <t>35475</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>52970</t>
+          <t>59958</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -9714,32 +9714,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12794</t>
+          <t>14383</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6458</t>
+          <t>7620</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22051</t>
+          <t>23979</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9749,32 +9749,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13193</t>
+          <t>13550</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8285</t>
+          <t>7866</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20021</t>
+          <t>20534</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9784,32 +9784,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>25987</t>
+          <t>27933</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17856</t>
+          <t>19072</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37031</t>
+          <t>39002</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>21,12%</t>
         </is>
       </c>
     </row>
@@ -9827,32 +9827,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>16751</t>
+          <t>18082</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8533</t>
+          <t>10840</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25530</t>
+          <t>29711</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9862,32 +9862,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>15281</t>
+          <t>16152</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9931</t>
+          <t>10495</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22081</t>
+          <t>24064</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9897,32 +9897,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>32032</t>
+          <t>34234</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>22839</t>
+          <t>24518</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>42470</t>
+          <t>45493</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>24,64%</t>
         </is>
       </c>
     </row>
@@ -9940,17 +9940,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>77014</t>
+          <t>93124</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>77014</t>
+          <t>93124</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>77014</t>
+          <t>93124</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9975,17 +9975,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>80824</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>80824</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>80824</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10010,17 +10010,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>157838</t>
+          <t>184655</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>157838</t>
+          <t>184655</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>157838</t>
+          <t>184655</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>29956</t>
+          <t>33322</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20648</t>
+          <t>23989</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41176</t>
+          <t>45098</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10092,32 +10092,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>22678</t>
+          <t>27221</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16520</t>
+          <t>19829</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30827</t>
+          <t>36304</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10127,32 +10127,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>52633</t>
+          <t>60542</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41525</t>
+          <t>47940</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>66284</t>
+          <t>74779</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>35,2%</t>
         </is>
       </c>
     </row>
@@ -10170,32 +10170,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>8391</t>
+          <t>8558</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16433</t>
+          <t>16497</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10205,32 +10205,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>14069</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7852</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>19457</t>
+          <t>20912</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10240,32 +10240,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>20885</t>
+          <t>22627</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>14053</t>
+          <t>14649</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>30472</t>
+          <t>32269</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -10283,32 +10283,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>31013</t>
+          <t>31854</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21750</t>
+          <t>21918</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>40833</t>
+          <t>42460</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10318,32 +10318,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>14283</t>
+          <t>15051</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8856</t>
+          <t>9878</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20584</t>
+          <t>22330</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10353,32 +10353,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>45296</t>
+          <t>46905</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>34894</t>
+          <t>36362</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>57663</t>
+          <t>59685</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>28,09%</t>
         </is>
       </c>
     </row>
@@ -10396,32 +10396,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>17416</t>
+          <t>19694</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10260</t>
+          <t>11765</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26969</t>
+          <t>28881</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10431,32 +10431,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>21464</t>
+          <t>21892</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14568</t>
+          <t>14249</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28738</t>
+          <t>29057</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10466,32 +10466,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>38880</t>
+          <t>41586</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28990</t>
+          <t>30845</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>51234</t>
+          <t>54766</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>25,78%</t>
         </is>
       </c>
     </row>
@@ -10509,32 +10509,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>20875</t>
+          <t>23350</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13460</t>
+          <t>15625</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>31058</t>
+          <t>33320</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10544,32 +10544,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>16085</t>
+          <t>17436</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11003</t>
+          <t>11600</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>25140</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10579,32 +10579,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>36960</t>
+          <t>40786</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>27394</t>
+          <t>30543</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>48545</t>
+          <t>52714</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,81%</t>
         </is>
       </c>
     </row>
@@ -10622,17 +10622,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>107650</t>
+          <t>116777</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>107650</t>
+          <t>116777</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>107650</t>
+          <t>116777</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10657,17 +10657,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>87004</t>
+          <t>95670</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>87004</t>
+          <t>95670</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>87004</t>
+          <t>95670</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10692,17 +10692,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>194653</t>
+          <t>212447</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>194653</t>
+          <t>212447</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>194653</t>
+          <t>212447</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>62842</t>
+          <t>78368</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20736</t>
+          <t>61369</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>107499</t>
+          <t>101520</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>72784</t>
+          <t>88201</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>60567</t>
+          <t>74055</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>88193</t>
+          <t>103959</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>135626</t>
+          <t>166569</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>66547</t>
+          <t>143565</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>189120</t>
+          <t>192029</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -10852,32 +10852,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>56812</t>
+          <t>62290</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>18382</t>
+          <t>46737</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>99146</t>
+          <t>82078</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10887,32 +10887,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>45819</t>
+          <t>52701</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>36178</t>
+          <t>42450</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>59361</t>
+          <t>66731</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10922,32 +10922,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>102632</t>
+          <t>114991</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>51962</t>
+          <t>93656</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>145582</t>
+          <t>136676</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -10965,32 +10965,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>124290</t>
+          <t>134444</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>43408</t>
+          <t>111535</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>209438</t>
+          <t>159888</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11000,32 +11000,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>93597</t>
+          <t>101164</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>80545</t>
+          <t>86884</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>109631</t>
+          <t>118365</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11035,32 +11035,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>217886</t>
+          <t>235608</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>103820</t>
+          <t>209894</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>297539</t>
+          <t>262709</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>30,21%</t>
         </is>
       </c>
     </row>
@@ -11078,32 +11078,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>76083</t>
+          <t>84181</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>28559</t>
+          <t>66955</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>128189</t>
+          <t>104297</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11113,32 +11113,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>66874</t>
+          <t>69818</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>55006</t>
+          <t>57080</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>80689</t>
+          <t>84021</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11148,32 +11148,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>142957</t>
+          <t>153999</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>69844</t>
+          <t>133198</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>194456</t>
+          <t>178800</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>20,56%</t>
         </is>
       </c>
     </row>
@@ -11191,32 +11191,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>348707</t>
+          <t>119083</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>155233</t>
+          <t>97049</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>556149</t>
+          <t>143344</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11226,32 +11226,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>71780</t>
+          <t>79286</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>58402</t>
+          <t>64088</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>86973</t>
+          <t>95334</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11261,32 +11261,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>420487</t>
+          <t>198369</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>222513</t>
+          <t>169776</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>704705</t>
+          <t>225364</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -11304,17 +11304,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>668734</t>
+          <t>478366</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>668734</t>
+          <t>478366</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>668734</t>
+          <t>478366</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11339,17 +11339,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>350855</t>
+          <t>391170</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>350855</t>
+          <t>391170</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>350855</t>
+          <t>391170</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11374,17 +11374,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1019589</t>
+          <t>869536</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1019589</t>
+          <t>869536</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1019589</t>
+          <t>869536</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
